--- a/resources/digital-products/files/dp-inter-scorecard.xlsx
+++ b/resources/digital-products/files/dp-inter-scorecard.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="£#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="11">
@@ -532,7 +532,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -598,7 +598,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Revenue (£)</t>
+          <t>Revenue ($)</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
@@ -677,7 +677,7 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>3 · Revenue per visitor (£)</t>
+          <t>3 · Revenue per visitor ($)</t>
         </is>
       </c>
       <c r="B17" s="12">
@@ -688,7 +688,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>4 · Average order value (£)</t>
+          <t>4 · Average order value ($)</t>
         </is>
       </c>
       <c r="B18" s="12">
@@ -721,7 +721,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>7 · Contribution per order (£)</t>
+          <t>7 · Contribution per order ($)</t>
         </is>
       </c>
       <c r="B21" s="12">
@@ -732,11 +732,11 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Contribution per visitor (£) — what you may spend to get one</t>
+          <t>Contribution per visitor ($) — what you may spend to get one</t>
         </is>
       </c>
       <c r="B22" s="13">
-        <f>IF(B6=0,"",((B8/B7)*(1-B12/100))*(B7/B6))</f>
+        <f>IF(B6=0,"",(B8/B6)*(1-B12/100))</f>
         <v/>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -776,5 +776,6 @@
     <mergeCell ref="A27:C27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/resources/digital-products/files/dp-inter-scorecard.xlsx
+++ b/resources/digital-products/files/dp-inter-scorecard.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -568,6 +568,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
@@ -645,6 +646,7 @@
         <v>6.5</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
@@ -745,6 +747,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
@@ -752,6 +755,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="14" t="n"/>
       <c r="B26" s="14" t="n"/>
@@ -764,12 +768,17 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
-        </is>
-      </c>
+          <t>ePORTS — your ecom source (eports.global)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
